--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="111">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/moped-ext-diagnoseKnoten</t>
+    <t>https://elga.moped.at/StructureDefinition/moped-ext-diagnoseKnoten</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -129,7 +129,10 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Element</t>
+    <t>element:https://elga.moped.at/StructureDefinition/MopedLKFRequest#Claim</t>
+  </si>
+  <si>
+    <t>element:https://elga.moped.at/StructureDefinition/MopedLKFResponse#ClaimResponse</t>
   </si>
   <si>
     <t>ID</t>
@@ -344,7 +347,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-LKFAbrechnungsKnoten-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-LKFAbrechnungsKnoten-valueset</t>
   </si>
   <si>
     <t xml:space="preserve">ext-1
@@ -486,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -653,6 +656,14 @@
       </c>
       <c r="B21" t="s" s="2">
         <v>38</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -690,7 +701,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.67578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -705,115 +716,115 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
@@ -829,10 +840,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -844,13 +855,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -904,16 +915,16 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>20</v>
@@ -921,10 +932,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -932,10 +943,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -947,13 +958,13 @@
         <v>20</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1004,30 +1015,30 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AJ3" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1035,10 +1046,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1050,13 +1061,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1095,31 +1106,31 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1127,10 +1138,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1138,10 +1149,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -1153,16 +1164,16 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1212,13 +1223,13 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
@@ -1227,15 +1238,15 @@
         <v>20</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1243,10 +1254,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1258,13 +1269,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1291,11 +1302,11 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -1313,22 +1324,22 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AK6" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI6" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:36:14+00:00</t>
+    <t>2025-02-20T20:13:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -347,7 +347,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://elga.moped.at/ValueSet/moped-LKFAbrechnungsKnoten-valueset</t>
+    <t>https://elga.moped.at/ValueSet/LKFAbrechnungsKnoten</t>
   </si>
   <si>
     <t xml:space="preserve">ext-1
@@ -701,7 +701,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.67578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.1796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:47:03+00:00</t>
+    <t>2025-03-01T14:53:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-diagnoseKnoten.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
